--- a/special unlocks/special unlocks.xlsx
+++ b/special unlocks/special unlocks.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iamal\OneDrive\Documents\GitHub\EWW\special unlocks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4402ec65308ce179/Documents/GitHub/EWW/special unlocks/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{D00B3435-118F-4929-A364-BD778DE76C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
